--- a/redis/sample/redis_sample.xlsx
+++ b/redis/sample/redis_sample.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6006" uniqueCount="1160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6006" uniqueCount="1071">
   <si>
     <t>prod_id</t>
   </si>
@@ -3243,281 +3243,14 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>25inchi-monitor</t>
-  </si>
-  <si>
-    <t>26inchi-monitor</t>
-  </si>
-  <si>
-    <t>27inchi-monitor</t>
-  </si>
-  <si>
-    <t>28inchi-monitor</t>
-  </si>
-  <si>
-    <t>29inchi-monitor</t>
-  </si>
-  <si>
-    <t>30inchi-monitor</t>
-  </si>
-  <si>
-    <t>31inchi-monitor</t>
-  </si>
-  <si>
-    <t>32inchi-monitor</t>
-  </si>
-  <si>
-    <t>33inchi-monitor</t>
-  </si>
-  <si>
-    <t>34inchi-monitor</t>
-  </si>
-  <si>
-    <t>35inchi-monitor</t>
-  </si>
-  <si>
-    <t>36inchi-monitor</t>
-  </si>
-  <si>
-    <t>37inchi-monitor</t>
-  </si>
-  <si>
-    <t>38inchi-monitor</t>
-  </si>
-  <si>
-    <t>39inchi-monitor</t>
-  </si>
-  <si>
-    <t>40inchi-monitor</t>
-  </si>
-  <si>
-    <t>41inchi-monitor</t>
-  </si>
-  <si>
-    <t>42inchi-monitor</t>
-  </si>
-  <si>
-    <t>43inchi-monitor</t>
-  </si>
-  <si>
-    <t>44inchi-monitor</t>
-  </si>
-  <si>
-    <t>45inchi-monitor</t>
-  </si>
-  <si>
-    <t>46inchi-monitor</t>
-  </si>
-  <si>
-    <t>47inchi-monitor</t>
-  </si>
-  <si>
-    <t>48inchi-monitor</t>
-  </si>
-  <si>
-    <t>49inchi-monitor</t>
-  </si>
-  <si>
-    <t>50inchi-monitor</t>
-  </si>
-  <si>
-    <t>51inchi-monitor</t>
-  </si>
-  <si>
-    <t>52inchi-monitor</t>
-  </si>
-  <si>
-    <t>53inchi-monitor</t>
-  </si>
-  <si>
-    <t>54inchi-monitor</t>
-  </si>
-  <si>
-    <t>55inchi-monitor</t>
-  </si>
-  <si>
-    <t>56inchi-monitor</t>
-  </si>
-  <si>
-    <t>57inchi-monitor</t>
-  </si>
-  <si>
-    <t>58inchi-monitor</t>
-  </si>
-  <si>
-    <t>59inchi-monitor</t>
-  </si>
-  <si>
-    <t>60inchi-monitor</t>
-  </si>
-  <si>
-    <t>61inchi-monitor</t>
-  </si>
-  <si>
-    <t>62inchi-monitor</t>
-  </si>
-  <si>
-    <t>63inchi-monitor</t>
-  </si>
-  <si>
-    <t>64inchi-monitor</t>
-  </si>
-  <si>
-    <t>65inchi-monitor</t>
-  </si>
-  <si>
-    <t>66inchi-monitor</t>
-  </si>
-  <si>
-    <t>67inchi-monitor</t>
-  </si>
-  <si>
-    <t>68inchi-monitor</t>
-  </si>
-  <si>
-    <t>69inchi-monitor</t>
-  </si>
-  <si>
-    <t>70inchi-monitor</t>
-  </si>
-  <si>
-    <t>71inchi-monitor</t>
-  </si>
-  <si>
-    <t>72inchi-monitor</t>
-  </si>
-  <si>
-    <t>73inchi-monitor</t>
-  </si>
-  <si>
-    <t>74inchi-monitor</t>
-  </si>
-  <si>
-    <t>75inchi-monitor</t>
-  </si>
-  <si>
-    <t>76inchi-monitor</t>
-  </si>
-  <si>
-    <t>77inchi-monitor</t>
-  </si>
-  <si>
-    <t>78inchi-monitor</t>
-  </si>
-  <si>
-    <t>79inchi-monitor</t>
-  </si>
-  <si>
-    <t>80inchi-monitor</t>
-  </si>
-  <si>
-    <t>81inchi-monitor</t>
-  </si>
-  <si>
-    <t>82inchi-monitor</t>
-  </si>
-  <si>
-    <t>83inchi-monitor</t>
-  </si>
-  <si>
-    <t>84inchi-monitor</t>
-  </si>
-  <si>
-    <t>85inchi-monitor</t>
-  </si>
-  <si>
-    <t>86inchi-monitor</t>
-  </si>
-  <si>
-    <t>87inchi-monitor</t>
-  </si>
-  <si>
-    <t>88inchi-monitor</t>
-  </si>
-  <si>
-    <t>89inchi-monitor</t>
-  </si>
-  <si>
-    <t>90inchi-monitor</t>
-  </si>
-  <si>
-    <t>91inchi-monitor</t>
-  </si>
-  <si>
-    <t>92inchi-monitor</t>
-  </si>
-  <si>
-    <t>93inchi-monitor</t>
-  </si>
-  <si>
-    <t>94inchi-monitor</t>
-  </si>
-  <si>
-    <t>95inchi-monitor</t>
-  </si>
-  <si>
-    <t>96inchi-monitor</t>
-  </si>
-  <si>
-    <t>97inchi-monitor</t>
-  </si>
-  <si>
-    <t>98inchi-monitor</t>
-  </si>
-  <si>
-    <t>99inchi-monitor</t>
-  </si>
-  <si>
-    <t>100inchi-monitor</t>
-  </si>
-  <si>
-    <t>101inchi-monitor</t>
-  </si>
-  <si>
-    <t>102inchi-monitor</t>
-  </si>
-  <si>
-    <t>103inchi-monitor</t>
-  </si>
-  <si>
-    <t>104inchi-monitor</t>
-  </si>
-  <si>
-    <t>105inchi-monitor</t>
-  </si>
-  <si>
-    <t>106inchi-monitor</t>
-  </si>
-  <si>
-    <t>107inchi-monitor</t>
-  </si>
-  <si>
-    <t>108inchi-monitor</t>
-  </si>
-  <si>
-    <t>109inchi-monitor</t>
-  </si>
-  <si>
-    <t>110inchi-monitor</t>
-  </si>
-  <si>
-    <t>111inchi-monitor</t>
-  </si>
-  <si>
-    <t>112inchi-monitor</t>
-  </si>
-  <si>
-    <t>113inchi-monitor</t>
-  </si>
-  <si>
-    <t>114inchi-monitor</t>
-  </si>
-  <si>
     <t>FPG0046</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>score</t>
+  </si>
+  <si>
+    <t>FPG0001</t>
   </si>
 </sst>
 </file>
@@ -3542,12 +3275,18 @@
       <charset val="129"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -3563,8 +3302,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="1"/>
@@ -3852,6 +3592,7 @@
     <col min="3" max="3" width="8.59765625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38.296875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="15.09765625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.796875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -3868,7 +3609,7 @@
         <v>1054</v>
       </c>
       <c r="H1" t="s">
-        <v>1159</v>
+        <v>1069</v>
       </c>
       <c r="I1" t="s">
         <v>1055</v>
@@ -3878,7 +3619,7 @@
       <c r="A2" t="s">
         <v>1052</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
         <v>1001</v>
       </c>
       <c r="C2">
@@ -3890,13 +3631,13 @@
       <c r="F2" t="s">
         <v>1053</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="1" t="s">
         <v>1056</v>
       </c>
       <c r="H2">
         <v>1.33</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" s="1" t="s">
         <v>1001</v>
       </c>
     </row>
@@ -4176,7 +3917,7 @@
       <c r="F13" t="s">
         <v>1053</v>
       </c>
-      <c r="G13" t="s">
+      <c r="G13" s="1" t="s">
         <v>1056</v>
       </c>
       <c r="H13">
@@ -4359,7 +4100,7 @@
         <v>1053</v>
       </c>
       <c r="G20" t="s">
-        <v>1068</v>
+        <v>1063</v>
       </c>
       <c r="H20">
         <v>1.75</v>
@@ -4462,7 +4203,7 @@
       <c r="F24" t="s">
         <v>1053</v>
       </c>
-      <c r="G24" t="s">
+      <c r="G24" s="1" t="s">
         <v>1056</v>
       </c>
       <c r="H24">
@@ -4645,7 +4386,7 @@
         <v>1053</v>
       </c>
       <c r="G31" t="s">
-        <v>1069</v>
+        <v>1063</v>
       </c>
       <c r="H31">
         <v>0.81</v>
@@ -4748,7 +4489,7 @@
       <c r="F35" t="s">
         <v>1053</v>
       </c>
-      <c r="G35" t="s">
+      <c r="G35" s="1" t="s">
         <v>1056</v>
       </c>
       <c r="H35">
@@ -4931,7 +4672,7 @@
         <v>1053</v>
       </c>
       <c r="G42" t="s">
-        <v>1070</v>
+        <v>1063</v>
       </c>
       <c r="H42">
         <v>0.61</v>
@@ -5034,7 +4775,7 @@
       <c r="F46" t="s">
         <v>1053</v>
       </c>
-      <c r="G46" t="s">
+      <c r="G46" s="1" t="s">
         <v>1056</v>
       </c>
       <c r="H46">
@@ -5067,7 +4808,7 @@
         <v>1.9</v>
       </c>
       <c r="I47" t="s">
-        <v>1158</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
@@ -5178,7 +4919,7 @@
       <c r="A52" t="s">
         <v>1052</v>
       </c>
-      <c r="B52" t="s">
+      <c r="B52" s="1" t="s">
         <v>1001</v>
       </c>
       <c r="C52">
@@ -5196,7 +4937,7 @@
       <c r="H52">
         <v>1.1100000000000001</v>
       </c>
-      <c r="I52" t="s">
+      <c r="I52" s="1" t="s">
         <v>1001</v>
       </c>
     </row>
@@ -5217,7 +4958,7 @@
         <v>1053</v>
       </c>
       <c r="G53" t="s">
-        <v>1071</v>
+        <v>1063</v>
       </c>
       <c r="H53">
         <v>0.65</v>
@@ -5320,7 +5061,7 @@
       <c r="F57" t="s">
         <v>1053</v>
       </c>
-      <c r="G57" t="s">
+      <c r="G57" s="1" t="s">
         <v>1056</v>
       </c>
       <c r="H57">
@@ -5503,7 +5244,7 @@
         <v>1053</v>
       </c>
       <c r="G64" t="s">
-        <v>1072</v>
+        <v>1063</v>
       </c>
       <c r="H64">
         <v>0.97</v>
@@ -5606,7 +5347,7 @@
       <c r="F68" t="s">
         <v>1053</v>
       </c>
-      <c r="G68" t="s">
+      <c r="G68" s="1" t="s">
         <v>1056</v>
       </c>
       <c r="H68">
@@ -5789,7 +5530,7 @@
         <v>1053</v>
       </c>
       <c r="G75" t="s">
-        <v>1073</v>
+        <v>1063</v>
       </c>
       <c r="H75">
         <v>1.62</v>
@@ -5892,7 +5633,7 @@
       <c r="F79" t="s">
         <v>1053</v>
       </c>
-      <c r="G79" t="s">
+      <c r="G79" s="1" t="s">
         <v>1056</v>
       </c>
       <c r="H79">
@@ -6075,7 +5816,7 @@
         <v>1053</v>
       </c>
       <c r="G86" t="s">
-        <v>1074</v>
+        <v>1063</v>
       </c>
       <c r="H86">
         <v>0.22</v>
@@ -6178,7 +5919,7 @@
       <c r="F90" t="s">
         <v>1053</v>
       </c>
-      <c r="G90" t="s">
+      <c r="G90" s="1" t="s">
         <v>1056</v>
       </c>
       <c r="H90">
@@ -6361,7 +6102,7 @@
         <v>1053</v>
       </c>
       <c r="G97" t="s">
-        <v>1075</v>
+        <v>1063</v>
       </c>
       <c r="H97">
         <v>0.22</v>
@@ -6464,7 +6205,7 @@
       <c r="F101" t="s">
         <v>1053</v>
       </c>
-      <c r="G101" t="s">
+      <c r="G101" s="1" t="s">
         <v>1056</v>
       </c>
       <c r="H101">
@@ -6478,7 +6219,7 @@
       <c r="A102" t="s">
         <v>1052</v>
       </c>
-      <c r="B102" t="s">
+      <c r="B102" s="1" t="s">
         <v>1001</v>
       </c>
       <c r="C102">
@@ -6496,7 +6237,7 @@
       <c r="H102">
         <v>0.49</v>
       </c>
-      <c r="I102" t="s">
+      <c r="I102" s="1" t="s">
         <v>1001</v>
       </c>
     </row>
@@ -6647,7 +6388,7 @@
         <v>1053</v>
       </c>
       <c r="G108" t="s">
-        <v>1076</v>
+        <v>1063</v>
       </c>
       <c r="H108">
         <v>0.89</v>
@@ -6750,7 +6491,7 @@
       <c r="F112" t="s">
         <v>1053</v>
       </c>
-      <c r="G112" t="s">
+      <c r="G112" s="1" t="s">
         <v>1056</v>
       </c>
       <c r="H112">
@@ -6933,7 +6674,7 @@
         <v>1053</v>
       </c>
       <c r="G119" t="s">
-        <v>1077</v>
+        <v>1063</v>
       </c>
       <c r="H119">
         <v>7.0000000000000007E-2</v>
@@ -7036,7 +6777,7 @@
       <c r="F123" t="s">
         <v>1053</v>
       </c>
-      <c r="G123" t="s">
+      <c r="G123" s="1" t="s">
         <v>1056</v>
       </c>
       <c r="H123">
@@ -7219,7 +6960,7 @@
         <v>1053</v>
       </c>
       <c r="G130" t="s">
-        <v>1078</v>
+        <v>1063</v>
       </c>
       <c r="H130">
         <v>0.28999999999999998</v>
@@ -7322,7 +7063,7 @@
       <c r="F134" t="s">
         <v>1053</v>
       </c>
-      <c r="G134" t="s">
+      <c r="G134" s="1" t="s">
         <v>1056</v>
       </c>
       <c r="H134">
@@ -7505,7 +7246,7 @@
         <v>1053</v>
       </c>
       <c r="G141" t="s">
-        <v>1079</v>
+        <v>1063</v>
       </c>
       <c r="H141">
         <v>0.69</v>
@@ -7608,7 +7349,7 @@
       <c r="F145" t="s">
         <v>1053</v>
       </c>
-      <c r="G145" t="s">
+      <c r="G145" s="1" t="s">
         <v>1056</v>
       </c>
       <c r="H145">
@@ -7778,7 +7519,7 @@
       <c r="A152" t="s">
         <v>1052</v>
       </c>
-      <c r="B152" t="s">
+      <c r="B152" s="1" t="s">
         <v>1001</v>
       </c>
       <c r="C152">
@@ -7791,12 +7532,12 @@
         <v>1053</v>
       </c>
       <c r="G152" t="s">
-        <v>1080</v>
+        <v>1063</v>
       </c>
       <c r="H152">
         <v>0.39</v>
       </c>
-      <c r="I152" t="s">
+      <c r="I152" s="1" t="s">
         <v>1001</v>
       </c>
     </row>
@@ -7894,7 +7635,7 @@
       <c r="F156" t="s">
         <v>1053</v>
       </c>
-      <c r="G156" t="s">
+      <c r="G156" s="1" t="s">
         <v>1056</v>
       </c>
       <c r="H156">
@@ -8077,7 +7818,7 @@
         <v>1053</v>
       </c>
       <c r="G163" t="s">
-        <v>1081</v>
+        <v>1063</v>
       </c>
       <c r="H163">
         <v>1.4</v>
@@ -8180,7 +7921,7 @@
       <c r="F167" t="s">
         <v>1053</v>
       </c>
-      <c r="G167" t="s">
+      <c r="G167" s="1" t="s">
         <v>1056</v>
       </c>
       <c r="H167">
@@ -8363,7 +8104,7 @@
         <v>1053</v>
       </c>
       <c r="G174" t="s">
-        <v>1082</v>
+        <v>1063</v>
       </c>
       <c r="H174">
         <v>0.7</v>
@@ -8466,7 +8207,7 @@
       <c r="F178" t="s">
         <v>1053</v>
       </c>
-      <c r="G178" t="s">
+      <c r="G178" s="1" t="s">
         <v>1056</v>
       </c>
       <c r="H178">
@@ -8649,7 +8390,7 @@
         <v>1053</v>
       </c>
       <c r="G185" t="s">
-        <v>1083</v>
+        <v>1063</v>
       </c>
       <c r="H185">
         <v>1.32</v>
@@ -8752,7 +8493,7 @@
       <c r="F189" t="s">
         <v>1053</v>
       </c>
-      <c r="G189" t="s">
+      <c r="G189" s="1" t="s">
         <v>1056</v>
       </c>
       <c r="H189">
@@ -8935,7 +8676,7 @@
         <v>1053</v>
       </c>
       <c r="G196" t="s">
-        <v>1084</v>
+        <v>1063</v>
       </c>
       <c r="H196">
         <v>0.47</v>
@@ -9038,7 +8779,7 @@
       <c r="F200" t="s">
         <v>1053</v>
       </c>
-      <c r="G200" t="s">
+      <c r="G200" s="1" t="s">
         <v>1056</v>
       </c>
       <c r="H200">
@@ -9078,7 +8819,7 @@
       <c r="A202" t="s">
         <v>1052</v>
       </c>
-      <c r="B202" t="s">
+      <c r="B202" s="1" t="s">
         <v>1001</v>
       </c>
       <c r="C202">
@@ -9096,7 +8837,7 @@
       <c r="H202">
         <v>0.37</v>
       </c>
-      <c r="I202" t="s">
+      <c r="I202" s="1" t="s">
         <v>1001</v>
       </c>
     </row>
@@ -9221,7 +8962,7 @@
         <v>1053</v>
       </c>
       <c r="G207" t="s">
-        <v>1085</v>
+        <v>1063</v>
       </c>
       <c r="H207">
         <v>1.07</v>
@@ -9507,7 +9248,7 @@
         <v>1053</v>
       </c>
       <c r="G218" t="s">
-        <v>1086</v>
+        <v>1063</v>
       </c>
       <c r="H218">
         <v>0.46</v>
@@ -9793,7 +9534,7 @@
         <v>1053</v>
       </c>
       <c r="G229" t="s">
-        <v>1087</v>
+        <v>1063</v>
       </c>
       <c r="H229">
         <v>0.7</v>
@@ -10079,7 +9820,7 @@
         <v>1053</v>
       </c>
       <c r="G240" t="s">
-        <v>1088</v>
+        <v>1063</v>
       </c>
       <c r="H240">
         <v>0.32</v>
@@ -10365,7 +10106,7 @@
         <v>1053</v>
       </c>
       <c r="G251" t="s">
-        <v>1089</v>
+        <v>1063</v>
       </c>
       <c r="H251">
         <v>0.41</v>
@@ -10378,7 +10119,7 @@
       <c r="A252" t="s">
         <v>1052</v>
       </c>
-      <c r="B252" t="s">
+      <c r="B252" s="1" t="s">
         <v>1001</v>
       </c>
       <c r="C252">
@@ -10396,7 +10137,7 @@
       <c r="H252">
         <v>0.72</v>
       </c>
-      <c r="I252" t="s">
+      <c r="I252" s="1" t="s">
         <v>1001</v>
       </c>
     </row>
@@ -10651,7 +10392,7 @@
         <v>1053</v>
       </c>
       <c r="G262" t="s">
-        <v>1090</v>
+        <v>1063</v>
       </c>
       <c r="H262">
         <v>1.26</v>
@@ -10937,7 +10678,7 @@
         <v>1053</v>
       </c>
       <c r="G273" t="s">
-        <v>1091</v>
+        <v>1063</v>
       </c>
       <c r="H273">
         <v>1.47</v>
@@ -11223,7 +10964,7 @@
         <v>1053</v>
       </c>
       <c r="G284" t="s">
-        <v>1092</v>
+        <v>1063</v>
       </c>
       <c r="H284">
         <v>0.62</v>
@@ -11509,7 +11250,7 @@
         <v>1053</v>
       </c>
       <c r="G295" t="s">
-        <v>1093</v>
+        <v>1063</v>
       </c>
       <c r="H295">
         <v>0.11</v>
@@ -11678,7 +11419,7 @@
       <c r="A302" t="s">
         <v>1052</v>
       </c>
-      <c r="B302" t="s">
+      <c r="B302" s="1" t="s">
         <v>1001</v>
       </c>
       <c r="C302">
@@ -11696,7 +11437,7 @@
       <c r="H302">
         <v>0.56000000000000005</v>
       </c>
-      <c r="I302" t="s">
+      <c r="I302" s="1" t="s">
         <v>1001</v>
       </c>
     </row>
@@ -11795,7 +11536,7 @@
         <v>1053</v>
       </c>
       <c r="G306" t="s">
-        <v>1094</v>
+        <v>1063</v>
       </c>
       <c r="H306">
         <v>0.93</v>
@@ -12081,7 +11822,7 @@
         <v>1053</v>
       </c>
       <c r="G317" t="s">
-        <v>1095</v>
+        <v>1063</v>
       </c>
       <c r="H317">
         <v>0.24</v>
@@ -12367,7 +12108,7 @@
         <v>1053</v>
       </c>
       <c r="G328" t="s">
-        <v>1096</v>
+        <v>1063</v>
       </c>
       <c r="H328">
         <v>1.1499999999999999</v>
@@ -12653,7 +12394,7 @@
         <v>1053</v>
       </c>
       <c r="G339" t="s">
-        <v>1097</v>
+        <v>1063</v>
       </c>
       <c r="H339">
         <v>0.4</v>
@@ -12939,7 +12680,7 @@
         <v>1053</v>
       </c>
       <c r="G350" t="s">
-        <v>1098</v>
+        <v>1063</v>
       </c>
       <c r="H350">
         <v>1.4</v>
@@ -12978,7 +12719,7 @@
       <c r="A352" t="s">
         <v>1052</v>
       </c>
-      <c r="B352" t="s">
+      <c r="B352" s="1" t="s">
         <v>1001</v>
       </c>
       <c r="C352">
@@ -12996,7 +12737,7 @@
       <c r="H352">
         <v>0.18</v>
       </c>
-      <c r="I352" t="s">
+      <c r="I352" s="1" t="s">
         <v>1001</v>
       </c>
     </row>
@@ -13225,7 +12966,7 @@
         <v>1053</v>
       </c>
       <c r="G361" t="s">
-        <v>1099</v>
+        <v>1063</v>
       </c>
       <c r="H361">
         <v>0.53</v>
@@ -13511,7 +13252,7 @@
         <v>1053</v>
       </c>
       <c r="G372" t="s">
-        <v>1100</v>
+        <v>1063</v>
       </c>
       <c r="H372">
         <v>1.99</v>
@@ -13797,7 +13538,7 @@
         <v>1053</v>
       </c>
       <c r="G383" t="s">
-        <v>1101</v>
+        <v>1063</v>
       </c>
       <c r="H383">
         <v>0.69</v>
@@ -13900,7 +13641,7 @@
       <c r="F387" t="s">
         <v>1053</v>
       </c>
-      <c r="G387" t="s">
+      <c r="G387" s="1" t="s">
         <v>1056</v>
       </c>
       <c r="H387">
@@ -14083,7 +13824,7 @@
         <v>1053</v>
       </c>
       <c r="G394" t="s">
-        <v>1102</v>
+        <v>1063</v>
       </c>
       <c r="H394">
         <v>0.94</v>
@@ -14186,7 +13927,7 @@
       <c r="F398" t="s">
         <v>1053</v>
       </c>
-      <c r="G398" t="s">
+      <c r="G398" s="1" t="s">
         <v>1056</v>
       </c>
       <c r="H398">
@@ -14278,7 +14019,7 @@
       <c r="A402" t="s">
         <v>1052</v>
       </c>
-      <c r="B402" t="s">
+      <c r="B402" s="1" t="s">
         <v>1001</v>
       </c>
       <c r="C402">
@@ -14296,7 +14037,7 @@
       <c r="H402">
         <v>0.25</v>
       </c>
-      <c r="I402" t="s">
+      <c r="I402" s="1" t="s">
         <v>1001</v>
       </c>
     </row>
@@ -14369,7 +14110,7 @@
         <v>1053</v>
       </c>
       <c r="G405" t="s">
-        <v>1103</v>
+        <v>1063</v>
       </c>
       <c r="H405">
         <v>1.74</v>
@@ -14472,7 +14213,7 @@
       <c r="F409" t="s">
         <v>1053</v>
       </c>
-      <c r="G409" t="s">
+      <c r="G409" s="1" t="s">
         <v>1056</v>
       </c>
       <c r="H409">
@@ -14655,7 +14396,7 @@
         <v>1053</v>
       </c>
       <c r="G416" t="s">
-        <v>1104</v>
+        <v>1063</v>
       </c>
       <c r="H416">
         <v>0.36</v>
@@ -14758,7 +14499,7 @@
       <c r="F420" t="s">
         <v>1053</v>
       </c>
-      <c r="G420" t="s">
+      <c r="G420" s="1" t="s">
         <v>1056</v>
       </c>
       <c r="H420">
@@ -14941,7 +14682,7 @@
         <v>1053</v>
       </c>
       <c r="G427" t="s">
-        <v>1105</v>
+        <v>1063</v>
       </c>
       <c r="H427">
         <v>1.49</v>
@@ -15044,7 +14785,7 @@
       <c r="F431" t="s">
         <v>1053</v>
       </c>
-      <c r="G431" t="s">
+      <c r="G431" s="1" t="s">
         <v>1056</v>
       </c>
       <c r="H431">
@@ -15227,7 +14968,7 @@
         <v>1053</v>
       </c>
       <c r="G438" t="s">
-        <v>1106</v>
+        <v>1063</v>
       </c>
       <c r="H438">
         <v>1.3</v>
@@ -15330,7 +15071,7 @@
       <c r="F442" t="s">
         <v>1053</v>
       </c>
-      <c r="G442" t="s">
+      <c r="G442" s="1" t="s">
         <v>1056</v>
       </c>
       <c r="H442">
@@ -15513,7 +15254,7 @@
         <v>1053</v>
       </c>
       <c r="G449" t="s">
-        <v>1107</v>
+        <v>1063</v>
       </c>
       <c r="H449">
         <v>0.55000000000000004</v>
@@ -15578,7 +15319,7 @@
       <c r="A452" t="s">
         <v>1052</v>
       </c>
-      <c r="B452" t="s">
+      <c r="B452" s="1" t="s">
         <v>1001</v>
       </c>
       <c r="C452">
@@ -15596,7 +15337,7 @@
       <c r="H452">
         <v>1.71</v>
       </c>
-      <c r="I452" t="s">
+      <c r="I452" s="1" t="s">
         <v>1001</v>
       </c>
     </row>
@@ -15616,7 +15357,7 @@
       <c r="F453" t="s">
         <v>1053</v>
       </c>
-      <c r="G453" t="s">
+      <c r="G453" s="1" t="s">
         <v>1056</v>
       </c>
       <c r="H453">
@@ -15799,7 +15540,7 @@
         <v>1053</v>
       </c>
       <c r="G460" t="s">
-        <v>1108</v>
+        <v>1063</v>
       </c>
       <c r="H460">
         <v>1.7</v>
@@ -15902,7 +15643,7 @@
       <c r="F464" t="s">
         <v>1053</v>
       </c>
-      <c r="G464" t="s">
+      <c r="G464" s="1" t="s">
         <v>1056</v>
       </c>
       <c r="H464">
@@ -16085,7 +15826,7 @@
         <v>1053</v>
       </c>
       <c r="G471" t="s">
-        <v>1109</v>
+        <v>1063</v>
       </c>
       <c r="H471">
         <v>1.78</v>
@@ -16188,7 +15929,7 @@
       <c r="F475" t="s">
         <v>1053</v>
       </c>
-      <c r="G475" t="s">
+      <c r="G475" s="1" t="s">
         <v>1056</v>
       </c>
       <c r="H475">
@@ -16371,7 +16112,7 @@
         <v>1053</v>
       </c>
       <c r="G482" t="s">
-        <v>1110</v>
+        <v>1063</v>
       </c>
       <c r="H482">
         <v>0.32</v>
@@ -16474,7 +16215,7 @@
       <c r="F486" t="s">
         <v>1053</v>
       </c>
-      <c r="G486" t="s">
+      <c r="G486" s="1" t="s">
         <v>1056</v>
       </c>
       <c r="H486">
@@ -16657,7 +16398,7 @@
         <v>1053</v>
       </c>
       <c r="G493" t="s">
-        <v>1111</v>
+        <v>1063</v>
       </c>
       <c r="H493">
         <v>1.23</v>
@@ -16760,7 +16501,7 @@
       <c r="F497" t="s">
         <v>1053</v>
       </c>
-      <c r="G497" t="s">
+      <c r="G497" s="1" t="s">
         <v>1056</v>
       </c>
       <c r="H497">
@@ -16878,7 +16619,7 @@
       <c r="A502" t="s">
         <v>1052</v>
       </c>
-      <c r="B502" t="s">
+      <c r="B502" s="1" t="s">
         <v>1001</v>
       </c>
       <c r="C502">
@@ -16896,7 +16637,7 @@
       <c r="H502">
         <v>0.97</v>
       </c>
-      <c r="I502" t="s">
+      <c r="I502" s="1" t="s">
         <v>1001</v>
       </c>
     </row>
@@ -16943,7 +16684,7 @@
         <v>1053</v>
       </c>
       <c r="G504" t="s">
-        <v>1112</v>
+        <v>1063</v>
       </c>
       <c r="H504">
         <v>1.86</v>
@@ -17046,7 +16787,7 @@
       <c r="F508" t="s">
         <v>1053</v>
       </c>
-      <c r="G508" t="s">
+      <c r="G508" s="1" t="s">
         <v>1056</v>
       </c>
       <c r="H508">
@@ -17229,7 +16970,7 @@
         <v>1053</v>
       </c>
       <c r="G515" t="s">
-        <v>1113</v>
+        <v>1063</v>
       </c>
       <c r="H515">
         <v>1.66</v>
@@ -17332,7 +17073,7 @@
       <c r="F519" t="s">
         <v>1053</v>
       </c>
-      <c r="G519" t="s">
+      <c r="G519" s="1" t="s">
         <v>1056</v>
       </c>
       <c r="H519">
@@ -17515,7 +17256,7 @@
         <v>1053</v>
       </c>
       <c r="G526" t="s">
-        <v>1114</v>
+        <v>1063</v>
       </c>
       <c r="H526">
         <v>0.71</v>
@@ -17618,7 +17359,7 @@
       <c r="F530" t="s">
         <v>1053</v>
       </c>
-      <c r="G530" t="s">
+      <c r="G530" s="1" t="s">
         <v>1056</v>
       </c>
       <c r="H530">
@@ -17801,7 +17542,7 @@
         <v>1053</v>
       </c>
       <c r="G537" t="s">
-        <v>1115</v>
+        <v>1063</v>
       </c>
       <c r="H537">
         <v>0.63</v>
@@ -17904,7 +17645,7 @@
       <c r="F541" t="s">
         <v>1053</v>
       </c>
-      <c r="G541" t="s">
+      <c r="G541" s="1" t="s">
         <v>1056</v>
       </c>
       <c r="H541">
@@ -18087,7 +17828,7 @@
         <v>1053</v>
       </c>
       <c r="G548" t="s">
-        <v>1116</v>
+        <v>1063</v>
       </c>
       <c r="H548">
         <v>1.25</v>
@@ -18178,7 +17919,7 @@
       <c r="A552" t="s">
         <v>1052</v>
       </c>
-      <c r="B552" t="s">
+      <c r="B552" s="1" t="s">
         <v>1001</v>
       </c>
       <c r="C552">
@@ -18190,13 +17931,13 @@
       <c r="F552" t="s">
         <v>1053</v>
       </c>
-      <c r="G552" t="s">
+      <c r="G552" s="1" t="s">
         <v>1056</v>
       </c>
       <c r="H552">
         <v>1.82</v>
       </c>
-      <c r="I552" t="s">
+      <c r="I552" s="1" t="s">
         <v>1001</v>
       </c>
     </row>
@@ -18373,7 +18114,7 @@
         <v>1053</v>
       </c>
       <c r="G559" t="s">
-        <v>1117</v>
+        <v>1063</v>
       </c>
       <c r="H559">
         <v>1.69</v>
@@ -18476,7 +18217,7 @@
       <c r="F563" t="s">
         <v>1053</v>
       </c>
-      <c r="G563" t="s">
+      <c r="G563" s="1" t="s">
         <v>1056</v>
       </c>
       <c r="H563">
@@ -18659,7 +18400,7 @@
         <v>1053</v>
       </c>
       <c r="G570" t="s">
-        <v>1118</v>
+        <v>1063</v>
       </c>
       <c r="H570">
         <v>1.06</v>
@@ -18762,7 +18503,7 @@
       <c r="F574" t="s">
         <v>1053</v>
       </c>
-      <c r="G574" t="s">
+      <c r="G574" s="1" t="s">
         <v>1056</v>
       </c>
       <c r="H574">
@@ -18945,7 +18686,7 @@
         <v>1053</v>
       </c>
       <c r="G581" t="s">
-        <v>1119</v>
+        <v>1063</v>
       </c>
       <c r="H581">
         <v>1.17</v>
@@ -19048,7 +18789,7 @@
       <c r="F585" t="s">
         <v>1053</v>
       </c>
-      <c r="G585" t="s">
+      <c r="G585" s="1" t="s">
         <v>1056</v>
       </c>
       <c r="H585">
@@ -19231,7 +18972,7 @@
         <v>1053</v>
       </c>
       <c r="G592" t="s">
-        <v>1120</v>
+        <v>1063</v>
       </c>
       <c r="H592">
         <v>1.25</v>
@@ -19334,7 +19075,7 @@
       <c r="F596" t="s">
         <v>1053</v>
       </c>
-      <c r="G596" t="s">
+      <c r="G596" s="1" t="s">
         <v>1056</v>
       </c>
       <c r="H596">
@@ -19478,7 +19219,7 @@
       <c r="A602" t="s">
         <v>1052</v>
       </c>
-      <c r="B602" t="s">
+      <c r="B602" s="1" t="s">
         <v>1001</v>
       </c>
       <c r="C602">
@@ -19496,7 +19237,7 @@
       <c r="H602">
         <v>0.61</v>
       </c>
-      <c r="I602" t="s">
+      <c r="I602" s="1" t="s">
         <v>1001</v>
       </c>
     </row>
@@ -19517,7 +19258,7 @@
         <v>1053</v>
       </c>
       <c r="G603" t="s">
-        <v>1121</v>
+        <v>1063</v>
       </c>
       <c r="H603">
         <v>1.51</v>
@@ -19620,7 +19361,7 @@
       <c r="F607" t="s">
         <v>1053</v>
       </c>
-      <c r="G607" t="s">
+      <c r="G607" s="1" t="s">
         <v>1056</v>
       </c>
       <c r="H607">
@@ -19803,7 +19544,7 @@
         <v>1053</v>
       </c>
       <c r="G614" t="s">
-        <v>1122</v>
+        <v>1063</v>
       </c>
       <c r="H614">
         <v>1.04</v>
@@ -19906,7 +19647,7 @@
       <c r="F618" t="s">
         <v>1053</v>
       </c>
-      <c r="G618" t="s">
+      <c r="G618" s="1" t="s">
         <v>1056</v>
       </c>
       <c r="H618">
@@ -20089,7 +19830,7 @@
         <v>1053</v>
       </c>
       <c r="G625" t="s">
-        <v>1123</v>
+        <v>1063</v>
       </c>
       <c r="H625">
         <v>0.18</v>
@@ -20192,7 +19933,7 @@
       <c r="F629" t="s">
         <v>1053</v>
       </c>
-      <c r="G629" t="s">
+      <c r="G629" s="1" t="s">
         <v>1056</v>
       </c>
       <c r="H629">
@@ -20375,7 +20116,7 @@
         <v>1053</v>
       </c>
       <c r="G636" t="s">
-        <v>1124</v>
+        <v>1063</v>
       </c>
       <c r="H636">
         <v>1.26</v>
@@ -20478,7 +20219,7 @@
       <c r="F640" t="s">
         <v>1053</v>
       </c>
-      <c r="G640" t="s">
+      <c r="G640" s="1" t="s">
         <v>1056</v>
       </c>
       <c r="H640">
@@ -20661,7 +20402,7 @@
         <v>1053</v>
       </c>
       <c r="G647" t="s">
-        <v>1125</v>
+        <v>1063</v>
       </c>
       <c r="H647">
         <v>1.59</v>
@@ -20764,7 +20505,7 @@
       <c r="F651" t="s">
         <v>1053</v>
       </c>
-      <c r="G651" t="s">
+      <c r="G651" s="1" t="s">
         <v>1056</v>
       </c>
       <c r="H651">
@@ -20778,7 +20519,7 @@
       <c r="A652" t="s">
         <v>1052</v>
       </c>
-      <c r="B652" t="s">
+      <c r="B652" s="1" t="s">
         <v>1001</v>
       </c>
       <c r="C652">
@@ -20796,7 +20537,7 @@
       <c r="H652">
         <v>0.42</v>
       </c>
-      <c r="I652" t="s">
+      <c r="I652" s="1" t="s">
         <v>1001</v>
       </c>
     </row>
@@ -20947,7 +20688,7 @@
         <v>1053</v>
       </c>
       <c r="G658" t="s">
-        <v>1126</v>
+        <v>1063</v>
       </c>
       <c r="H658">
         <v>1.2</v>
@@ -21050,7 +20791,7 @@
       <c r="F662" t="s">
         <v>1053</v>
       </c>
-      <c r="G662" t="s">
+      <c r="G662" s="1" t="s">
         <v>1056</v>
       </c>
       <c r="H662">
@@ -21233,7 +20974,7 @@
         <v>1053</v>
       </c>
       <c r="G669" t="s">
-        <v>1127</v>
+        <v>1063</v>
       </c>
       <c r="H669">
         <v>0.95</v>
@@ -21336,7 +21077,7 @@
       <c r="F673" t="s">
         <v>1053</v>
       </c>
-      <c r="G673" t="s">
+      <c r="G673" s="1" t="s">
         <v>1056</v>
       </c>
       <c r="H673">
@@ -21519,7 +21260,7 @@
         <v>1053</v>
       </c>
       <c r="G680" t="s">
-        <v>1128</v>
+        <v>1063</v>
       </c>
       <c r="H680">
         <v>1.17</v>
@@ -21622,7 +21363,7 @@
       <c r="F684" t="s">
         <v>1053</v>
       </c>
-      <c r="G684" t="s">
+      <c r="G684" s="1" t="s">
         <v>1056</v>
       </c>
       <c r="H684">
@@ -21805,7 +21546,7 @@
         <v>1053</v>
       </c>
       <c r="G691" t="s">
-        <v>1129</v>
+        <v>1063</v>
       </c>
       <c r="H691">
         <v>0.56000000000000005</v>
@@ -21908,7 +21649,7 @@
       <c r="F695" t="s">
         <v>1053</v>
       </c>
-      <c r="G695" t="s">
+      <c r="G695" s="1" t="s">
         <v>1056</v>
       </c>
       <c r="H695">
@@ -22078,7 +21819,7 @@
       <c r="A702" t="s">
         <v>1052</v>
       </c>
-      <c r="B702" t="s">
+      <c r="B702" s="1" t="s">
         <v>1001</v>
       </c>
       <c r="C702">
@@ -22091,12 +21832,12 @@
         <v>1053</v>
       </c>
       <c r="G702" t="s">
-        <v>1130</v>
+        <v>1063</v>
       </c>
       <c r="H702">
         <v>1.51</v>
       </c>
-      <c r="I702" t="s">
+      <c r="I702" s="1" t="s">
         <v>1001</v>
       </c>
     </row>
@@ -22194,7 +21935,7 @@
       <c r="F706" t="s">
         <v>1053</v>
       </c>
-      <c r="G706" t="s">
+      <c r="G706" s="1" t="s">
         <v>1056</v>
       </c>
       <c r="H706">
@@ -22377,7 +22118,7 @@
         <v>1053</v>
       </c>
       <c r="G713" t="s">
-        <v>1131</v>
+        <v>1063</v>
       </c>
       <c r="H713">
         <v>1.07</v>
@@ -22480,7 +22221,7 @@
       <c r="F717" t="s">
         <v>1053</v>
       </c>
-      <c r="G717" t="s">
+      <c r="G717" s="1" t="s">
         <v>1056</v>
       </c>
       <c r="H717">
@@ -22663,7 +22404,7 @@
         <v>1053</v>
       </c>
       <c r="G724" t="s">
-        <v>1132</v>
+        <v>1063</v>
       </c>
       <c r="H724">
         <v>0.01</v>
@@ -22766,7 +22507,7 @@
       <c r="F728" t="s">
         <v>1053</v>
       </c>
-      <c r="G728" t="s">
+      <c r="G728" s="1" t="s">
         <v>1056</v>
       </c>
       <c r="H728">
@@ -22949,7 +22690,7 @@
         <v>1053</v>
       </c>
       <c r="G735" t="s">
-        <v>1133</v>
+        <v>1063</v>
       </c>
       <c r="H735">
         <v>1.46</v>
@@ -23052,7 +22793,7 @@
       <c r="F739" t="s">
         <v>1053</v>
       </c>
-      <c r="G739" t="s">
+      <c r="G739" s="1" t="s">
         <v>1056</v>
       </c>
       <c r="H739">
@@ -23235,7 +22976,7 @@
         <v>1053</v>
       </c>
       <c r="G746" t="s">
-        <v>1134</v>
+        <v>1063</v>
       </c>
       <c r="H746">
         <v>1.38</v>
@@ -23338,7 +23079,7 @@
       <c r="F750" t="s">
         <v>1053</v>
       </c>
-      <c r="G750" t="s">
+      <c r="G750" s="1" t="s">
         <v>1056</v>
       </c>
       <c r="H750">
@@ -23378,7 +23119,7 @@
       <c r="A752" t="s">
         <v>1052</v>
       </c>
-      <c r="B752" t="s">
+      <c r="B752" s="1" t="s">
         <v>1001</v>
       </c>
       <c r="C752">
@@ -23396,7 +23137,7 @@
       <c r="H752">
         <v>1.74</v>
       </c>
-      <c r="I752" t="s">
+      <c r="I752" s="1" t="s">
         <v>1001</v>
       </c>
     </row>
@@ -23521,7 +23262,7 @@
         <v>1053</v>
       </c>
       <c r="G757" t="s">
-        <v>1135</v>
+        <v>1063</v>
       </c>
       <c r="H757">
         <v>0.65</v>
@@ -23624,7 +23365,7 @@
       <c r="F761" t="s">
         <v>1053</v>
       </c>
-      <c r="G761" t="s">
+      <c r="G761" s="1" t="s">
         <v>1056</v>
       </c>
       <c r="H761">
@@ -23807,7 +23548,7 @@
         <v>1053</v>
       </c>
       <c r="G768" t="s">
-        <v>1136</v>
+        <v>1063</v>
       </c>
       <c r="H768">
         <v>1.32</v>
@@ -23910,7 +23651,7 @@
       <c r="F772" t="s">
         <v>1053</v>
       </c>
-      <c r="G772" t="s">
+      <c r="G772" s="1" t="s">
         <v>1056</v>
       </c>
       <c r="H772">
@@ -24093,7 +23834,7 @@
         <v>1053</v>
       </c>
       <c r="G779" t="s">
-        <v>1137</v>
+        <v>1063</v>
       </c>
       <c r="H779">
         <v>0.25</v>
@@ -24196,7 +23937,7 @@
       <c r="F783" t="s">
         <v>1053</v>
       </c>
-      <c r="G783" t="s">
+      <c r="G783" s="1" t="s">
         <v>1056</v>
       </c>
       <c r="H783">
@@ -24379,7 +24120,7 @@
         <v>1053</v>
       </c>
       <c r="G790" t="s">
-        <v>1138</v>
+        <v>1063</v>
       </c>
       <c r="H790">
         <v>1.64</v>
@@ -24482,7 +24223,7 @@
       <c r="F794" t="s">
         <v>1053</v>
       </c>
-      <c r="G794" t="s">
+      <c r="G794" s="1" t="s">
         <v>1056</v>
       </c>
       <c r="H794">
@@ -24665,7 +24406,7 @@
         <v>1053</v>
       </c>
       <c r="G801" t="s">
-        <v>1139</v>
+        <v>1063</v>
       </c>
       <c r="H801">
         <v>1.64</v>
@@ -24678,7 +24419,7 @@
       <c r="A802" t="s">
         <v>1052</v>
       </c>
-      <c r="B802" t="s">
+      <c r="B802" s="1" t="s">
         <v>1001</v>
       </c>
       <c r="C802">
@@ -24696,7 +24437,7 @@
       <c r="H802">
         <v>0.67</v>
       </c>
-      <c r="I802" t="s">
+      <c r="I802" s="1" t="s">
         <v>1001</v>
       </c>
     </row>
@@ -24768,7 +24509,7 @@
       <c r="F805" t="s">
         <v>1053</v>
       </c>
-      <c r="G805" t="s">
+      <c r="G805" s="1" t="s">
         <v>1056</v>
       </c>
       <c r="H805">
@@ -24951,7 +24692,7 @@
         <v>1053</v>
       </c>
       <c r="G812" t="s">
-        <v>1140</v>
+        <v>1063</v>
       </c>
       <c r="H812">
         <v>1.78</v>
@@ -25054,7 +24795,7 @@
       <c r="F816" t="s">
         <v>1053</v>
       </c>
-      <c r="G816" t="s">
+      <c r="G816" s="1" t="s">
         <v>1056</v>
       </c>
       <c r="H816">
@@ -25237,7 +24978,7 @@
         <v>1053</v>
       </c>
       <c r="G823" t="s">
-        <v>1141</v>
+        <v>1063</v>
       </c>
       <c r="H823">
         <v>0.01</v>
@@ -25340,7 +25081,7 @@
       <c r="F827" t="s">
         <v>1053</v>
       </c>
-      <c r="G827" t="s">
+      <c r="G827" s="1" t="s">
         <v>1056</v>
       </c>
       <c r="H827">
@@ -25523,7 +25264,7 @@
         <v>1053</v>
       </c>
       <c r="G834" t="s">
-        <v>1142</v>
+        <v>1063</v>
       </c>
       <c r="H834">
         <v>0.38</v>
@@ -25626,7 +25367,7 @@
       <c r="F838" t="s">
         <v>1053</v>
       </c>
-      <c r="G838" t="s">
+      <c r="G838" s="1" t="s">
         <v>1056</v>
       </c>
       <c r="H838">
@@ -25809,7 +25550,7 @@
         <v>1053</v>
       </c>
       <c r="G845" t="s">
-        <v>1143</v>
+        <v>1063</v>
       </c>
       <c r="H845">
         <v>1.65</v>
@@ -25912,7 +25653,7 @@
       <c r="F849" t="s">
         <v>1053</v>
       </c>
-      <c r="G849" t="s">
+      <c r="G849" s="1" t="s">
         <v>1056</v>
       </c>
       <c r="H849">
@@ -25978,7 +25719,7 @@
       <c r="A852" t="s">
         <v>1052</v>
       </c>
-      <c r="B852" t="s">
+      <c r="B852" s="1" t="s">
         <v>1001</v>
       </c>
       <c r="C852">
@@ -25996,7 +25737,7 @@
       <c r="H852">
         <v>1.06</v>
       </c>
-      <c r="I852" t="s">
+      <c r="I852" s="1" t="s">
         <v>1001</v>
       </c>
     </row>
@@ -26095,7 +25836,7 @@
         <v>1053</v>
       </c>
       <c r="G856" t="s">
-        <v>1144</v>
+        <v>1063</v>
       </c>
       <c r="H856">
         <v>0.62</v>
@@ -26198,7 +25939,7 @@
       <c r="F860" t="s">
         <v>1053</v>
       </c>
-      <c r="G860" t="s">
+      <c r="G860" s="1" t="s">
         <v>1056</v>
       </c>
       <c r="H860">
@@ -26381,7 +26122,7 @@
         <v>1053</v>
       </c>
       <c r="G867" t="s">
-        <v>1145</v>
+        <v>1063</v>
       </c>
       <c r="H867">
         <v>0.36</v>
@@ -26484,7 +26225,7 @@
       <c r="F871" t="s">
         <v>1053</v>
       </c>
-      <c r="G871" t="s">
+      <c r="G871" s="1" t="s">
         <v>1056</v>
       </c>
       <c r="H871">
@@ -26667,7 +26408,7 @@
         <v>1053</v>
       </c>
       <c r="G878" t="s">
-        <v>1146</v>
+        <v>1063</v>
       </c>
       <c r="H878">
         <v>1.83</v>
@@ -26770,7 +26511,7 @@
       <c r="F882" t="s">
         <v>1053</v>
       </c>
-      <c r="G882" t="s">
+      <c r="G882" s="1" t="s">
         <v>1056</v>
       </c>
       <c r="H882">
@@ -26953,7 +26694,7 @@
         <v>1053</v>
       </c>
       <c r="G889" t="s">
-        <v>1147</v>
+        <v>1063</v>
       </c>
       <c r="H889">
         <v>0.53</v>
@@ -27056,7 +26797,7 @@
       <c r="F893" t="s">
         <v>1053</v>
       </c>
-      <c r="G893" t="s">
+      <c r="G893" s="1" t="s">
         <v>1056</v>
       </c>
       <c r="H893">
@@ -27239,7 +26980,7 @@
         <v>1053</v>
       </c>
       <c r="G900" t="s">
-        <v>1148</v>
+        <v>1063</v>
       </c>
       <c r="H900">
         <v>1.1399999999999999</v>
@@ -27278,7 +27019,7 @@
       <c r="A902" t="s">
         <v>1052</v>
       </c>
-      <c r="B902" t="s">
+      <c r="B902" s="1" t="s">
         <v>1001</v>
       </c>
       <c r="C902">
@@ -27296,7 +27037,7 @@
       <c r="H902">
         <v>1.24</v>
       </c>
-      <c r="I902" t="s">
+      <c r="I902" s="1" t="s">
         <v>1001</v>
       </c>
     </row>
@@ -27342,7 +27083,7 @@
       <c r="F904" t="s">
         <v>1053</v>
       </c>
-      <c r="G904" t="s">
+      <c r="G904" s="1" t="s">
         <v>1056</v>
       </c>
       <c r="H904">
@@ -27525,7 +27266,7 @@
         <v>1053</v>
       </c>
       <c r="G911" t="s">
-        <v>1149</v>
+        <v>1063</v>
       </c>
       <c r="H911">
         <v>0.99</v>
@@ -27628,7 +27369,7 @@
       <c r="F915" t="s">
         <v>1053</v>
       </c>
-      <c r="G915" t="s">
+      <c r="G915" s="1" t="s">
         <v>1056</v>
       </c>
       <c r="H915">
@@ -27811,7 +27552,7 @@
         <v>1053</v>
       </c>
       <c r="G922" t="s">
-        <v>1150</v>
+        <v>1063</v>
       </c>
       <c r="H922">
         <v>1.26</v>
@@ -27914,7 +27655,7 @@
       <c r="F926" t="s">
         <v>1053</v>
       </c>
-      <c r="G926" t="s">
+      <c r="G926" s="1" t="s">
         <v>1056</v>
       </c>
       <c r="H926">
@@ -28097,7 +27838,7 @@
         <v>1053</v>
       </c>
       <c r="G933" t="s">
-        <v>1151</v>
+        <v>1063</v>
       </c>
       <c r="H933">
         <v>1.08</v>
@@ -28200,7 +27941,7 @@
       <c r="F937" t="s">
         <v>1053</v>
       </c>
-      <c r="G937" t="s">
+      <c r="G937" s="1" t="s">
         <v>1056</v>
       </c>
       <c r="H937">
@@ -28383,7 +28124,7 @@
         <v>1053</v>
       </c>
       <c r="G944" t="s">
-        <v>1152</v>
+        <v>1063</v>
       </c>
       <c r="H944">
         <v>1.96</v>
@@ -28486,7 +28227,7 @@
       <c r="F948" t="s">
         <v>1053</v>
       </c>
-      <c r="G948" t="s">
+      <c r="G948" s="1" t="s">
         <v>1056</v>
       </c>
       <c r="H948">
@@ -28578,7 +28319,7 @@
       <c r="A952" t="s">
         <v>1052</v>
       </c>
-      <c r="B952" t="s">
+      <c r="B952" s="1" t="s">
         <v>1001</v>
       </c>
       <c r="C952">
@@ -28596,8 +28337,8 @@
       <c r="H952">
         <v>1.33</v>
       </c>
-      <c r="I952" t="s">
-        <v>1001</v>
+      <c r="I952" s="1" t="s">
+        <v>1070</v>
       </c>
     </row>
     <row r="953" spans="1:9" x14ac:dyDescent="0.25">
@@ -28669,7 +28410,7 @@
         <v>1053</v>
       </c>
       <c r="G955" t="s">
-        <v>1153</v>
+        <v>1063</v>
       </c>
       <c r="H955">
         <v>0.28999999999999998</v>
@@ -28772,7 +28513,7 @@
       <c r="F959" t="s">
         <v>1053</v>
       </c>
-      <c r="G959" t="s">
+      <c r="G959" s="1" t="s">
         <v>1056</v>
       </c>
       <c r="H959">
@@ -28955,7 +28696,7 @@
         <v>1053</v>
       </c>
       <c r="G966" t="s">
-        <v>1154</v>
+        <v>1063</v>
       </c>
       <c r="H966">
         <v>0.72</v>
@@ -29058,7 +28799,7 @@
       <c r="F970" t="s">
         <v>1053</v>
       </c>
-      <c r="G970" t="s">
+      <c r="G970" s="1" t="s">
         <v>1056</v>
       </c>
       <c r="H970">
@@ -29241,7 +28982,7 @@
         <v>1053</v>
       </c>
       <c r="G977" t="s">
-        <v>1155</v>
+        <v>1063</v>
       </c>
       <c r="H977">
         <v>1.63</v>
@@ -29344,7 +29085,7 @@
       <c r="F981" t="s">
         <v>1053</v>
       </c>
-      <c r="G981" t="s">
+      <c r="G981" s="1" t="s">
         <v>1056</v>
       </c>
       <c r="H981">
@@ -29527,7 +29268,7 @@
         <v>1053</v>
       </c>
       <c r="G988" t="s">
-        <v>1156</v>
+        <v>1063</v>
       </c>
       <c r="H988">
         <v>1.62</v>
@@ -29630,7 +29371,7 @@
       <c r="F992" t="s">
         <v>1053</v>
       </c>
-      <c r="G992" t="s">
+      <c r="G992" s="1" t="s">
         <v>1056</v>
       </c>
       <c r="H992">
@@ -29813,7 +29554,7 @@
         <v>1053</v>
       </c>
       <c r="G999" t="s">
-        <v>1157</v>
+        <v>1063</v>
       </c>
       <c r="H999">
         <v>1.46</v>
